--- a/Docs/Risk Assessment.xlsx
+++ b/Docs/Risk Assessment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_639EBC300292C4990A28FE19CF245AEF9223F918" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19D0CF42-7408-4154-89DB-E958EA108246}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_639EBC300292C4990A28FE19CF245AEF9223F918" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C5E5867-F5D6-4D55-9B9E-4F48CB0C9267}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,6 +547,32 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -554,33 +580,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1084,101 +1084,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="26"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
     </row>
     <row r="3" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="21"/>
+      <c r="E4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="17" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="28"/>
-      <c r="K4" s="25" t="s">
+      <c r="H4" s="21"/>
+      <c r="I4" s="15"/>
+      <c r="K4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="23" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="24" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="28"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="15"/>
       <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
@@ -1194,11 +1194,11 @@
       <c r="K7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
     </row>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
@@ -1684,6 +1684,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="L5:N5"/>
@@ -1693,11 +1698,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E4:F4"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:I18">
     <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
@@ -1736,14 +1736,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
